--- a/test/zipupload.xlsx
+++ b/test/zipupload.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DDA5B3-858E-4D68-92DC-E89C98BE1FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11ACBEBE-0F5F-496B-858F-8781DA7FDC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{821D1EAA-1C88-42BF-895F-F2A05B9FA2D9}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>File1</t>
   </si>
@@ -37,6 +37,12 @@
   </si>
   <si>
     <t>C:\Users\Abhiraj Das\Downloads\DMS-Frontend-main.zip</t>
+  </si>
+  <si>
+    <t>TypeofData</t>
+  </si>
+  <si>
+    <t>Zip Files</t>
   </si>
 </sst>
 </file>
@@ -388,23 +394,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981F7557-E867-4D4D-B495-82132341CA54}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
